--- a/data/trans_bre/IP07B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-11,08</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19,4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-14,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32,29%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.807271993067596</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-11.08219179829578</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.64915338244614</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>19.40088069301033</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.0574471855091999</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1495677919099911</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2295752612649877</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3228807728943777</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,64; 19,01</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-30,36; 6,17</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,12; 31,21</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2,15; 37,11</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-8,54; 25,73</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-36,35; 9,28</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,13; 47,87</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3,14; 79,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.642895846417971</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-30.36251018795336</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5.116758427138697</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2.146568601294532</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.08542685347492686</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3635296552648879</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.06126871799473002</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0.03139358166503178</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.01342768600837</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.166497556579695</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>31.20587246096405</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>37.10931703488185</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.2573004964552317</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.09280576187344594</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.4787358603869528</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.7914106197102866</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-15,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-14,66</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,95%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-21,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-18,55; 18,09</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-31,06; -0,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,13; 13,74</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-35,35; 6,54</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-21,91; 26,51</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-34,05; -0,8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-12,47; 18,57</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-47,79; 10,79</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.7336417965053688</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-15.71411079277668</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.143902306457611</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-14.65860993906858</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.009469552096197049</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.178470807041353</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.01366371337863896</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2181191148733991</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,71</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,9</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-16,34</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-6,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-23,95%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-18.5546629863515</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-31.05549704301306</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-11.13044460415549</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-35.34787658017567</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2190815366099332</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3404848018576933</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1246541480587868</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4778626308730994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-23,51; 10,85</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-21,36; 11,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-11,88; 19,97</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-41,53; 14,91</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-29,28; 14,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-24,55; 17,0</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-13,41; 27,75</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-55,3; 28,12</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>18.08629081085417</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.4585568433109657</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>13.74361932280783</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.5371356302261</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2651108659166985</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.007999337926022386</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1857387916922483</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1079246334481665</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.71379623985867</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.898354833062313</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.44071875847405</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-16.34020964763705</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.07528284007130946</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.06130522934405518</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.06703406184626107</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2395476721892213</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-16,6; 6,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,0; 16,74</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,75; 10,77</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,79; 26,81</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-20,48; 8,95</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-9,51; 26,48</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-9,36; 15,06</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-10,63; 54,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-23.50537937861863</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-21.36364620632967</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-11.88327390294544</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-41.53214998743029</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.2928122995810746</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.245493042251178</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1341453411699414</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5529589329389135</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10.85125152662827</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.82803926067092</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>19.97480358170085</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.91050145084321</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1481137169054741</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.170013590474588</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.2775480651643443</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2811724551427205</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>17,84</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,88</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>20,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>27,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-4,6%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>44,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,02; 30,64</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-9,65; 17,43</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-14,48; 6,44</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 42,57</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 54,61</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-13,0; 28,37</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,0; 8,17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 137,9</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-5.396486974519576</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.347793782502808</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.473854484752046</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.750628842854326</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.07065748092765647</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.078439325303921</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01869735072940869</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1574056256408982</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-3,64</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-11,87</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-8,45</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6,89</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-4,43%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-15,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-9,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-16.60048890626155</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.004390378139099</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.749996351789491</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.793781325489062</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2048004698597402</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.09512801709853465</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.09359853648244867</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1063278379209331</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-18,57; 12,24</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-34,28; 9,1</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-24,04; 4,81</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-12,95; 26,43</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-21,01; 16,73</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-42,95; 12,66</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-25,55; 5,24</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-16,81; 48,01</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.371741189763831</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>16.74261207054918</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.76616471372761</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>26.81223709004673</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.08951008063959383</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.264806506304692</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.150550185224534</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5463841024879391</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,57</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-3,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12,59%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>17.83506781656964</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.161363474024781</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.879225618726156</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>20.63800739671109</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.2748030894545793</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.04567176143751722</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.04595377564717199</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.4401086624595898</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,89; 7,39</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-8,37; 3,99</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 6,47</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 16,4</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-4,97; 10,2</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-11,03; 5,66</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-4,78; 8,13</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-3,0; 30,14</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3.020287993281243</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-9.654381644607737</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-14.48392050582639</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.08384088353105638</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.04235395912289888</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1300498542449166</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1600207156172877</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0.0015850329658219</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>30.64183607864214</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>17.43492994607494</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.436433197820317</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>42.56955612196462</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5460982158501442</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2836598465098826</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.08169284792596038</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.378992639836324</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-3.642172129621746</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-11.86927999364384</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-8.451778444836389</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>6.886557916295589</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.04427055489457303</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1584637878802463</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.09253823242951456</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0.1043381115008523</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-18.56898983481706</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-34.28451143100192</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-24.03534001897767</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-12.9488600567559</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.2101426089348354</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.4295059919513179</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.2554630304350319</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.1680962407903052</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>12.23821691005921</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>9.098192586200431</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>4.810249076233479</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>26.42818114996364</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1672953670803733</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.1265619032969997</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.05244874591866867</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.4800631692738735</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.788458139921878</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-2.224245390618007</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1.034257974916653</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>7.572985582660574</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.02369296904885415</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.0303139128172412</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.01257777127560973</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.1258614399858698</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.8852935654466</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-8.37161499386329</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-4.060424146578214</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.972930588583189</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.04971227796069939</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.1102783095613978</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.0477571079978751</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.0299991466062274</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>7.38712017209476</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.990794280362366</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>6.47237399534395</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>16.39850847016673</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.1020146823327496</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.05657182227401435</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.08134464914861993</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.30144902816484</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
